--- a/Data/Hires/Workday_NewHire_Portugal_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Portugal_Regression_PK17.xlsx
@@ -1,23 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{EA24CA3D-F727-4FAA-BE7B-11E83322F987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BY$53</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="122">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -214,12 +229,6 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699017</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>420 Recruitment (Gozyb Sosobo (10034456))</t>
   </si>
   <si>
@@ -353,9 +362,6 @@
   </si>
   <si>
     <t>Test_2</t>
-  </si>
-  <si>
-    <t>10699025</t>
   </si>
   <si>
     <t>420 Store Management (Rilyv Zisozy (4206015))</t>
@@ -397,92 +403,92 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color indexed="12"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="7"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
       <family val="3"/>
-      <sz val="7"/>
-      <name val="Courier New"/>
     </font>
     <font>
+      <sz val="10"/>
       <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -505,7 +511,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -522,7 +528,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,24 +548,42 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -953,89 +977,89 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BZ76"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
-    <col min="5" max="5" width="7.77734375" customWidth="1"/>
-    <col min="6" max="6" width="15.21875" customWidth="1"/>
+    <col min="5" max="5" width="7.81640625" customWidth="1"/>
+    <col min="6" max="6" width="15.1796875" customWidth="1"/>
     <col min="7" max="7" width="41" customWidth="1"/>
-    <col min="8" max="8" width="5.6640625" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" customWidth="1"/>
-    <col min="11" max="11" width="5.88671875" customWidth="1"/>
-    <col min="12" max="12" width="12.109375" customWidth="1"/>
-    <col min="13" max="13" width="7.77734375" customWidth="1"/>
-    <col min="14" max="14" width="21.6640625" customWidth="1"/>
-    <col min="15" max="15" width="10.21875" customWidth="1"/>
-    <col min="16" max="16" width="6.77734375" customWidth="1"/>
-    <col min="17" max="17" width="5.88671875" customWidth="1"/>
-    <col min="18" max="18" width="12.6640625" customWidth="1"/>
-    <col min="19" max="19" width="18.6640625" customWidth="1"/>
-    <col min="20" max="20" width="5.88671875" customWidth="1"/>
-    <col min="21" max="21" width="10.5546875" customWidth="1"/>
-    <col min="22" max="22" width="8.5546875" customWidth="1"/>
-    <col min="23" max="23" width="23.33203125" customWidth="1"/>
-    <col min="24" max="24" width="14.44140625" customWidth="1"/>
-    <col min="25" max="25" width="24.33203125" customWidth="1"/>
-    <col min="26" max="26" width="8.88671875" customWidth="1"/>
-    <col min="27" max="27" width="16.21875" style="1" customWidth="1"/>
-    <col min="28" max="28" width="20.21875" customWidth="1"/>
-    <col min="29" max="29" width="23.88671875" style="1" customWidth="1"/>
-    <col min="30" max="30" width="9.109375" customWidth="1"/>
-    <col min="31" max="31" width="18.33203125" customWidth="1"/>
-    <col min="32" max="32" width="19.5546875" customWidth="1"/>
-    <col min="33" max="33" width="16.88671875" customWidth="1"/>
-    <col min="34" max="34" width="20.5546875" customWidth="1"/>
-    <col min="35" max="35" width="31.21875" customWidth="1"/>
-    <col min="36" max="36" width="46.109375" customWidth="1"/>
-    <col min="37" max="37" width="23.5546875" customWidth="1"/>
+    <col min="8" max="8" width="5.6328125" customWidth="1"/>
+    <col min="9" max="9" width="12.6328125" customWidth="1"/>
+    <col min="10" max="10" width="11.54296875" customWidth="1"/>
+    <col min="11" max="11" width="5.90625" customWidth="1"/>
+    <col min="12" max="12" width="12.08984375" customWidth="1"/>
+    <col min="13" max="13" width="7.81640625" customWidth="1"/>
+    <col min="14" max="14" width="21.6328125" customWidth="1"/>
+    <col min="15" max="15" width="10.1796875" customWidth="1"/>
+    <col min="16" max="16" width="6.81640625" customWidth="1"/>
+    <col min="17" max="17" width="5.90625" customWidth="1"/>
+    <col min="18" max="18" width="12.6328125" customWidth="1"/>
+    <col min="19" max="19" width="18.6328125" customWidth="1"/>
+    <col min="20" max="20" width="5.90625" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" customWidth="1"/>
+    <col min="22" max="22" width="8.54296875" customWidth="1"/>
+    <col min="23" max="23" width="23.36328125" customWidth="1"/>
+    <col min="24" max="24" width="14.453125" customWidth="1"/>
+    <col min="25" max="25" width="24.36328125" customWidth="1"/>
+    <col min="26" max="26" width="8.90625" customWidth="1"/>
+    <col min="27" max="27" width="16.1796875" style="1" customWidth="1"/>
+    <col min="28" max="28" width="20.1796875" customWidth="1"/>
+    <col min="29" max="29" width="23.90625" style="1" customWidth="1"/>
+    <col min="30" max="30" width="9.08984375" customWidth="1"/>
+    <col min="31" max="31" width="18.36328125" customWidth="1"/>
+    <col min="32" max="32" width="19.54296875" customWidth="1"/>
+    <col min="33" max="33" width="16.90625" customWidth="1"/>
+    <col min="34" max="34" width="20.54296875" customWidth="1"/>
+    <col min="35" max="35" width="31.1796875" customWidth="1"/>
+    <col min="36" max="36" width="46.08984375" customWidth="1"/>
+    <col min="37" max="37" width="23.54296875" customWidth="1"/>
     <col min="38" max="38" width="16" style="1" customWidth="1"/>
     <col min="39" max="39" width="16" customWidth="1"/>
-    <col min="40" max="40" width="44.21875" customWidth="1"/>
+    <col min="40" max="40" width="44.1796875" customWidth="1"/>
     <col min="41" max="41" width="6" customWidth="1"/>
-    <col min="42" max="42" width="28.44140625" customWidth="1"/>
-    <col min="43" max="43" width="15.109375" customWidth="1"/>
+    <col min="42" max="42" width="28.453125" customWidth="1"/>
+    <col min="43" max="43" width="15.08984375" customWidth="1"/>
     <col min="44" max="44" width="12" customWidth="1"/>
-    <col min="45" max="45" width="20.77734375" customWidth="1"/>
-    <col min="46" max="46" width="27.6640625" customWidth="1"/>
-    <col min="48" max="48" width="6.88671875" customWidth="1"/>
-    <col min="49" max="49" width="10.77734375" customWidth="1"/>
-    <col min="50" max="50" width="13.44140625" customWidth="1"/>
-    <col min="51" max="51" width="12.44140625" customWidth="1"/>
+    <col min="45" max="45" width="20.81640625" customWidth="1"/>
+    <col min="46" max="46" width="27.6328125" customWidth="1"/>
+    <col min="48" max="48" width="6.90625" customWidth="1"/>
+    <col min="49" max="49" width="10.81640625" customWidth="1"/>
+    <col min="50" max="50" width="13.453125" customWidth="1"/>
+    <col min="51" max="51" width="12.453125" customWidth="1"/>
     <col min="52" max="52" width="10" customWidth="1"/>
-    <col min="53" max="53" width="11.88671875" customWidth="1"/>
-    <col min="54" max="54" width="15.88671875" customWidth="1"/>
-    <col min="55" max="55" width="16.33203125" customWidth="1"/>
-    <col min="56" max="56" width="8.44140625" customWidth="1"/>
-    <col min="57" max="57" width="36.88671875" customWidth="1"/>
+    <col min="53" max="53" width="11.90625" customWidth="1"/>
+    <col min="54" max="54" width="15.90625" customWidth="1"/>
+    <col min="55" max="55" width="16.36328125" customWidth="1"/>
+    <col min="56" max="56" width="8.453125" customWidth="1"/>
+    <col min="57" max="57" width="36.90625" customWidth="1"/>
     <col min="58" max="58" width="12" customWidth="1"/>
-    <col min="59" max="59" width="8.44140625" customWidth="1"/>
-    <col min="60" max="60" width="22.33203125" customWidth="1"/>
+    <col min="59" max="59" width="8.453125" customWidth="1"/>
+    <col min="60" max="60" width="22.36328125" customWidth="1"/>
     <col min="61" max="61" width="10" customWidth="1"/>
-    <col min="62" max="62" width="8.44140625" customWidth="1"/>
-    <col min="63" max="63" width="20.109375" customWidth="1"/>
+    <col min="62" max="62" width="8.453125" customWidth="1"/>
+    <col min="63" max="63" width="20.08984375" customWidth="1"/>
     <col min="64" max="64" width="15" customWidth="1"/>
-    <col min="65" max="65" width="13.77734375" customWidth="1"/>
-    <col min="66" max="66" width="11.5546875" customWidth="1"/>
-    <col min="67" max="67" width="26.44140625" customWidth="1"/>
+    <col min="65" max="65" width="13.81640625" customWidth="1"/>
+    <col min="66" max="66" width="11.54296875" customWidth="1"/>
+    <col min="67" max="67" width="26.453125" customWidth="1"/>
     <col min="68" max="68" width="17" customWidth="1"/>
-    <col min="69" max="69" width="16.33203125" customWidth="1"/>
-    <col min="70" max="70" width="10.109375" customWidth="1"/>
-    <col min="71" max="71" width="21.6640625" customWidth="1"/>
-    <col min="72" max="72" width="12.21875" customWidth="1"/>
-    <col min="73" max="73" width="15.109375" customWidth="1"/>
-    <col min="74" max="74" width="5.21875" customWidth="1"/>
-    <col min="75" max="75" width="6.33203125" customWidth="1"/>
-    <col min="76" max="76" width="23.21875" customWidth="1"/>
-    <col min="77" max="77" width="22.33203125" customWidth="1"/>
+    <col min="69" max="69" width="16.36328125" customWidth="1"/>
+    <col min="70" max="70" width="10.08984375" customWidth="1"/>
+    <col min="71" max="71" width="21.6328125" customWidth="1"/>
+    <col min="72" max="72" width="12.1796875" customWidth="1"/>
+    <col min="73" max="73" width="15.08984375" customWidth="1"/>
+    <col min="74" max="74" width="5.1796875" customWidth="1"/>
+    <col min="75" max="75" width="6.36328125" customWidth="1"/>
+    <col min="76" max="76" width="23.1796875" customWidth="1"/>
+    <col min="77" max="77" width="22.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.4" customHeight="1" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:77" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1238,212 +1262,208 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="E2" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="F2" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="G2" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="H2" s="17" t="s">
         <v>69</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>71</v>
       </c>
       <c r="I2" s="18">
         <v>234456532</v>
       </c>
       <c r="J2" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="19">
+        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
+        <v>45761</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="N2" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="O2" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="L2" s="19">
-        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45755</v>
-      </c>
-      <c r="M2" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="N2" s="20" t="s">
+      <c r="P2" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="Q2" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="R2" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="P2" s="20" t="s">
+      <c r="S2" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="Q2" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="R2" s="21" t="s">
+      <c r="T2" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="U2" s="19">
+        <f t="shared" ref="U2:U3" ca="1" si="1">L2</f>
+        <v>45761</v>
+      </c>
+      <c r="V2" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="S2" s="22" t="s">
+      <c r="W2" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="T2" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="U2" s="19">
-        <f t="shared" ref="U2:U3" si="1">L2</f>
-        <v>45755</v>
-      </c>
-      <c r="V2" s="18" t="s">
+      <c r="X2" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="W2" s="23" t="s">
+      <c r="Y2" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="X2" s="21" t="s">
+      <c r="Z2" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="Y2" s="24" t="s">
+      <c r="AA2" s="25" t="s">
         <v>82</v>
-      </c>
-      <c r="Z2" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA2" s="25" t="s">
-        <v>84</v>
       </c>
       <c r="AB2" s="14">
         <v>40</v>
       </c>
       <c r="AC2" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD2" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE2" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="AD2" s="14" t="s">
+      <c r="AF2" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="AE2" s="19" t="s">
+      <c r="AG2" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="AF2" s="18" t="s">
+      <c r="AH2" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="AG2" s="27" t="s">
+      <c r="AI2" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="AH2" s="18" t="s">
+      <c r="AJ2" s="28" t="s">
         <v>90</v>
-      </c>
-      <c r="AI2" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ2" s="28" t="s">
-        <v>92</v>
       </c>
       <c r="AK2" s="18">
         <v>99</v>
       </c>
       <c r="AL2" s="21">
-        <f t="shared" ref="AL2:AL3" si="2">TODAY()+60</f>
-        <v>45846</v>
+        <f t="shared" ref="AL2:AL3" ca="1" si="2">TODAY()+60</f>
+        <v>45852</v>
       </c>
       <c r="AM2" s="21">
-        <f t="shared" ref="AM2:AM3" si="3">U2</f>
-        <v>45755</v>
+        <f t="shared" ref="AM2:AM3" ca="1" si="3">U2</f>
+        <v>45761</v>
       </c>
       <c r="AN2" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO2" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP2" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="AO2" s="20" t="s">
+      <c r="AQ2" s="19" t="str">
+        <f t="shared" ref="AQ2:AQ3" si="4">AE2</f>
+        <v>N/A</v>
+      </c>
+      <c r="AR2" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="AP2" s="21" t="s">
+      <c r="AS2" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="AQ2" s="19">
-        <f t="shared" ref="AQ2:AQ3" si="4">AE2</f>
-        <v>NaN</v>
-      </c>
-      <c r="AR2" s="14" t="s">
+      <c r="AT2" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="AS2" s="14" t="s">
+      <c r="AU2" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="AV2" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="AT2" s="14" t="s">
+      <c r="AW2" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="AU2" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="AV2" s="30" t="s">
+      <c r="AX2" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="AY2" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="AW2" s="21" t="s">
+      <c r="AZ2" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA2" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="AX2" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="AY2" s="30" t="s">
+      <c r="BB2" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="AZ2" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="BA2" s="31" t="s">
+      <c r="BC2" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD2" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="BE2" s="32" t="s">
         <v>102</v>
-      </c>
-      <c r="BB2" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="BC2" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="BD2" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="BE2" s="32" t="s">
-        <v>104</v>
       </c>
       <c r="BF2" s="33">
         <v>10000895673</v>
       </c>
       <c r="BG2" s="32" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="BH2" s="32" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BI2" s="33">
         <v>100845873</v>
       </c>
       <c r="BJ2" s="32" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="BK2" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="BL2" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="BM2" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="BL2" s="35" t="s">
+      <c r="BN2" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="BM2" s="32" t="s">
+      <c r="BO2" s="32" t="s">
         <v>108</v>
-      </c>
-      <c r="BN2" s="32" t="s">
-        <v>109</v>
-      </c>
-      <c r="BO2" s="32" t="s">
-        <v>110</v>
       </c>
       <c r="BP2" s="12"/>
       <c r="BQ2" s="12"/>
@@ -1456,212 +1476,208 @@
       <c r="BX2" s="12"/>
       <c r="BY2" s="12"/>
     </row>
-    <row r="3" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="G3" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" s="13" t="s">
+      <c r="H3" s="17" t="s">
         <v>113</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>116</v>
       </c>
       <c r="I3" s="18">
         <v>234456532</v>
       </c>
       <c r="J3" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="L3" s="19">
+        <f t="shared" ca="1" si="0"/>
+        <v>45761</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="N3" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="K3" s="18" t="s">
+      <c r="O3" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="L3" s="19">
-        <f t="shared" si="0"/>
-        <v>45755</v>
-      </c>
-      <c r="M3" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="N3" s="20" t="s">
+      <c r="P3" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="Q3" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="R3" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="P3" s="20" t="s">
+      <c r="S3" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="Q3" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="R3" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="S3" s="22" t="s">
-        <v>78</v>
-      </c>
       <c r="T3" s="18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="U3" s="19">
-        <f t="shared" si="1"/>
-        <v>45755</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>45761</v>
       </c>
       <c r="V3" s="18" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="W3" s="23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="X3" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y3" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z3" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="Y3" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z3" s="21" t="s">
-        <v>83</v>
-      </c>
       <c r="AA3" s="25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AB3" s="14">
         <v>40</v>
       </c>
       <c r="AC3" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD3" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE3" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="AD3" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE3" s="19" t="s">
-        <v>87</v>
-      </c>
       <c r="AF3" s="18" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="AG3" s="37">
         <v>251</v>
       </c>
       <c r="AH3" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI3" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ3" s="28" t="s">
         <v>90</v>
-      </c>
-      <c r="AI3" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ3" s="28" t="s">
-        <v>92</v>
       </c>
       <c r="AK3" s="18">
         <v>99</v>
       </c>
       <c r="AL3" s="21">
-        <f t="shared" si="2"/>
-        <v>45846</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45852</v>
       </c>
       <c r="AM3" s="21">
-        <f t="shared" si="3"/>
-        <v>45755</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>45761</v>
       </c>
       <c r="AN3" s="29" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="AO3" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP3" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="AQ3" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>N/A</v>
+      </c>
+      <c r="AR3" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="AP3" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="AQ3" s="19">
-        <f t="shared" si="4"/>
-        <v>NaN</v>
-      </c>
-      <c r="AR3" s="14" t="s">
-        <v>96</v>
-      </c>
       <c r="AS3" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AT3" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AU3" s="14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AV3" s="30" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AW3" s="21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AX3" s="30" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AY3" s="30" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AZ3" s="30" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="BA3" s="31" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="BB3" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="BC3" s="31" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="BD3" s="32" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="BE3" s="32" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="BF3" s="33">
         <v>10000895671</v>
       </c>
       <c r="BG3" s="32" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="BH3" s="32" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="BI3" s="33">
         <v>100845871</v>
       </c>
       <c r="BJ3" s="32" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="BK3" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="BL3" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="BM3" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="BL3" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="BM3" s="32" t="s">
+      <c r="BN3" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="BO3" s="32" t="s">
         <v>108</v>
-      </c>
-      <c r="BN3" s="32" t="s">
-        <v>109</v>
-      </c>
-      <c r="BO3" s="32" t="s">
-        <v>110</v>
       </c>
       <c r="BP3" s="12"/>
       <c r="BQ3" s="12"/>
@@ -1674,7 +1690,7 @@
       <c r="BX3" s="12"/>
       <c r="BY3" s="12"/>
     </row>
-    <row r="4" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="36"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -1753,7 +1769,7 @@
       <c r="BX4" s="12"/>
       <c r="BY4" s="12"/>
     </row>
-    <row r="5" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="36"/>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
@@ -1832,7 +1848,7 @@
       <c r="BX5" s="12"/>
       <c r="BY5" s="12"/>
     </row>
-    <row r="6" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="36"/>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -1910,7 +1926,7 @@
       <c r="BX6" s="12"/>
       <c r="BY6" s="12"/>
     </row>
-    <row r="7" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="36"/>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -1989,7 +2005,7 @@
       <c r="BX7" s="12"/>
       <c r="BY7" s="12"/>
     </row>
-    <row r="8" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="36"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -2068,7 +2084,7 @@
       <c r="BX8" s="12"/>
       <c r="BY8" s="12"/>
     </row>
-    <row r="9" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="36"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -2147,7 +2163,7 @@
       <c r="BX9" s="12"/>
       <c r="BY9" s="12"/>
     </row>
-    <row r="10" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="36"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -2226,7 +2242,7 @@
       <c r="BX10" s="12"/>
       <c r="BY10" s="12"/>
     </row>
-    <row r="11" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="36"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -2305,7 +2321,7 @@
       <c r="BX11" s="12"/>
       <c r="BY11" s="12"/>
     </row>
-    <row r="12" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="36"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -2384,7 +2400,7 @@
       <c r="BX12" s="12"/>
       <c r="BY12" s="12"/>
     </row>
-    <row r="13" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="36"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -2463,7 +2479,7 @@
       <c r="BX13" s="12"/>
       <c r="BY13" s="12"/>
     </row>
-    <row r="14" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="36"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -2542,7 +2558,7 @@
       <c r="BX14" s="12"/>
       <c r="BY14" s="12"/>
     </row>
-    <row r="15" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="36"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -2621,7 +2637,7 @@
       <c r="BX15" s="12"/>
       <c r="BY15" s="12"/>
     </row>
-    <row r="16" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="36"/>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
@@ -2700,7 +2716,7 @@
       <c r="BX16" s="12"/>
       <c r="BY16" s="12"/>
     </row>
-    <row r="17" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="12"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -2780,7 +2796,7 @@
       <c r="BY17" s="12"/>
       <c r="BZ17" s="12"/>
     </row>
-    <row r="18" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="12"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
@@ -2860,7 +2876,7 @@
       <c r="BY18" s="12"/>
       <c r="BZ18" s="12"/>
     </row>
-    <row r="19" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
@@ -2940,7 +2956,7 @@
       <c r="BY19" s="12"/>
       <c r="BZ19" s="12"/>
     </row>
-    <row r="20" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="12"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -3020,7 +3036,7 @@
       <c r="BY20" s="12"/>
       <c r="BZ20" s="12"/>
     </row>
-    <row r="21" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -3100,7 +3116,7 @@
       <c r="BY21" s="12"/>
       <c r="BZ21" s="12"/>
     </row>
-    <row r="22" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="12"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -3180,7 +3196,7 @@
       <c r="BY22" s="12"/>
       <c r="BZ22" s="12"/>
     </row>
-    <row r="23" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="12"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -3260,7 +3276,7 @@
       <c r="BY23" s="12"/>
       <c r="BZ23" s="12"/>
     </row>
-    <row r="24" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="12"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -3340,7 +3356,7 @@
       <c r="BY24" s="12"/>
       <c r="BZ24" s="12"/>
     </row>
-    <row r="25" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -3420,7 +3436,7 @@
       <c r="BY25" s="12"/>
       <c r="BZ25" s="12"/>
     </row>
-    <row r="26" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -3500,7 +3516,7 @@
       <c r="BY26" s="12"/>
       <c r="BZ26" s="12"/>
     </row>
-    <row r="27" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
@@ -3580,7 +3596,7 @@
       <c r="BY27" s="12"/>
       <c r="BZ27" s="12"/>
     </row>
-    <row r="28" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="12"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
@@ -3660,7 +3676,7 @@
       <c r="BY28" s="12"/>
       <c r="BZ28" s="12"/>
     </row>
-    <row r="29" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="12"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -3740,7 +3756,7 @@
       <c r="BY29" s="12"/>
       <c r="BZ29" s="12"/>
     </row>
-    <row r="30" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="12"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -3820,7 +3836,7 @@
       <c r="BY30" s="12"/>
       <c r="BZ30" s="12"/>
     </row>
-    <row r="31" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="12"/>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
@@ -3900,7 +3916,7 @@
       <c r="BY31" s="12"/>
       <c r="BZ31" s="12"/>
     </row>
-    <row r="32" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="12"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
@@ -3980,7 +3996,7 @@
       <c r="BY32" s="12"/>
       <c r="BZ32" s="12"/>
     </row>
-    <row r="33" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="12"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -4060,7 +4076,7 @@
       <c r="BY33" s="12"/>
       <c r="BZ33" s="12"/>
     </row>
-    <row r="34" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="12"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
@@ -4140,7 +4156,7 @@
       <c r="BY34" s="12"/>
       <c r="BZ34" s="12"/>
     </row>
-    <row r="35" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="12"/>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
@@ -4220,7 +4236,7 @@
       <c r="BY35" s="12"/>
       <c r="BZ35" s="12"/>
     </row>
-    <row r="36" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="12"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -4300,7 +4316,7 @@
       <c r="BY36" s="12"/>
       <c r="BZ36" s="12"/>
     </row>
-    <row r="37" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
@@ -4380,7 +4396,7 @@
       <c r="BY37" s="12"/>
       <c r="BZ37" s="12"/>
     </row>
-    <row r="38" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="12"/>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
@@ -4460,7 +4476,7 @@
       <c r="BY38" s="12"/>
       <c r="BZ38" s="12"/>
     </row>
-    <row r="39" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="12"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
@@ -4540,7 +4556,7 @@
       <c r="BY39" s="12"/>
       <c r="BZ39" s="12"/>
     </row>
-    <row r="40" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="12"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -4620,7 +4636,7 @@
       <c r="BY40" s="12"/>
       <c r="BZ40" s="12"/>
     </row>
-    <row r="41" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="12"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -4700,7 +4716,7 @@
       <c r="BY41" s="12"/>
       <c r="BZ41" s="12"/>
     </row>
-    <row r="42" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="12"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
@@ -4780,7 +4796,7 @@
       <c r="BY42" s="12"/>
       <c r="BZ42" s="12"/>
     </row>
-    <row r="43" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="12"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
@@ -4860,7 +4876,7 @@
       <c r="BY43" s="12"/>
       <c r="BZ43" s="12"/>
     </row>
-    <row r="44" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="12"/>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
@@ -4940,7 +4956,7 @@
       <c r="BY44" s="12"/>
       <c r="BZ44" s="12"/>
     </row>
-    <row r="45" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="12"/>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
@@ -5020,7 +5036,7 @@
       <c r="BY45" s="12"/>
       <c r="BZ45" s="12"/>
     </row>
-    <row r="46" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="12"/>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
@@ -5100,7 +5116,7 @@
       <c r="BY46" s="12"/>
       <c r="BZ46" s="12"/>
     </row>
-    <row r="47" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="12"/>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
@@ -5180,7 +5196,7 @@
       <c r="BY47" s="12"/>
       <c r="BZ47" s="12"/>
     </row>
-    <row r="48" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="12"/>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
@@ -5260,7 +5276,7 @@
       <c r="BY48" s="12"/>
       <c r="BZ48" s="12"/>
     </row>
-    <row r="49" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="12"/>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
@@ -5340,7 +5356,7 @@
       <c r="BY49" s="12"/>
       <c r="BZ49" s="12"/>
     </row>
-    <row r="50" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="12"/>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
@@ -5420,7 +5436,7 @@
       <c r="BY50" s="12"/>
       <c r="BZ50" s="12"/>
     </row>
-    <row r="51" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="12"/>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
@@ -5500,7 +5516,7 @@
       <c r="BY51" s="12"/>
       <c r="BZ51" s="12"/>
     </row>
-    <row r="52" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="12"/>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
@@ -5580,7 +5596,7 @@
       <c r="BY52" s="12"/>
       <c r="BZ52" s="12"/>
     </row>
-    <row r="53" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="12"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -5660,7 +5676,7 @@
       <c r="BY53" s="12"/>
       <c r="BZ53" s="12"/>
     </row>
-    <row r="54" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:78" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="12"/>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
@@ -5740,78 +5756,78 @@
       <c r="BY54" s="12"/>
       <c r="BZ54" s="12"/>
     </row>
-    <row r="55" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F55" s="12"/>
     </row>
-    <row r="56" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F56" s="12"/>
     </row>
-    <row r="57" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F57" s="12"/>
     </row>
-    <row r="58" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F58" s="12"/>
     </row>
-    <row r="59" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F59" s="12"/>
     </row>
-    <row r="60" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F60" s="12"/>
     </row>
-    <row r="61" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F61" s="12"/>
     </row>
-    <row r="62" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F62" s="12"/>
     </row>
-    <row r="63" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F63" s="12"/>
     </row>
-    <row r="64" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F64" s="12"/>
     </row>
-    <row r="65" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F65" s="12"/>
     </row>
-    <row r="66" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F66" s="12"/>
     </row>
-    <row r="67" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F67" s="12"/>
     </row>
-    <row r="68" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F68" s="12"/>
     </row>
-    <row r="69" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F69" s="12"/>
     </row>
-    <row r="70" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F70" s="12"/>
     </row>
-    <row r="71" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F71" s="12"/>
     </row>
-    <row r="72" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F72" s="12"/>
     </row>
-    <row r="73" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F73" s="12"/>
     </row>
-    <row r="74" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F74" s="12"/>
     </row>
-    <row r="75" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F75" s="12"/>
     </row>
-    <row r="76" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F76" s="12"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S2" r:id="rId1"/>
-    <hyperlink ref="S3" r:id="rId2"/>
+    <hyperlink ref="S2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="S3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_Portugal_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Portugal_Regression_PK17.xlsx
@@ -1,38 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{EA24CA3D-F727-4FAA-BE7B-11E83322F987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BY$53</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="125">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -229,6 +214,15 @@
     <t>Test_1</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Kyler Abernathy' Employee:{undefined}TimeoutError: page.goto: Timeout 30000ms exceeded.
+Call log:
+  [2m- navigating to "https://wd3-impl.workday.com/wday/authgwy/primark17/login.htmld", waiting until "load"[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
     <t>420 Recruitment (Gozyb Sosobo (10034456))</t>
   </si>
   <si>
@@ -364,6 +358,14 @@
     <t>Test_2</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Harry Herzog' Employee:{}Error: locator.focus: Error: strict mode violation: getByLabel('Country', { exact: true }) resolved to 2 elements:
+    1) &lt;input value="" dir="ltr" tabindex="0" autocomplete="of…/&gt; aka getByRole('row', { name: 'Remove Row Country Gozyb' }).getByLabel('Country')
+    2) &lt;input value="" dir="ltr" tabindex="0" autocomplete="of…/&gt; aka getByRole('row', { name: 'Remove Row Country National' }).getByLabel('Country', { exact: true })
+Call log:
+  [2m- waiting for getByLabel('Country', { exact: true })[22m
+</t>
+  </si>
+  <si>
     <t>420 Store Management (Rilyv Zisozy (4206015))</t>
   </si>
   <si>
@@ -379,7 +381,7 @@
     <t>New</t>
   </si>
   <si>
-    <t>Auto 90099085</t>
+    <t>Auto 1265429</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -403,95 +405,95 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color indexed="8"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
+      <color indexed="12"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color indexed="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF1F1F1F"/>
+      <family val="3"/>
       <sz val="7"/>
-      <color rgb="FF1F1F1F"/>
       <name val="Courier New"/>
-      <family val="3"/>
     </font>
     <font>
-      <sz val="10"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -511,7 +513,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -523,12 +525,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,42 +545,24 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -621,7 +600,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -630,7 +609,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -651,7 +630,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -977,9 +956,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BZ76"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.36328125" customWidth="1"/>
     <col min="2" max="2" width="11.08984375" customWidth="1"/>
@@ -1059,7 +1038,7 @@
     <col min="77" max="77" width="22.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" ht="17.4" customHeight="1" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1262,208 +1241,212 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
+      <c r="B2" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>66</v>
+      </c>
       <c r="D2" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I2" s="18">
         <v>234456532</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K2" s="18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L2" s="19">
-        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
+        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
         <v>45761</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N2" s="20" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O2" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="P2" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q2" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="P2" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q2" s="18" t="s">
-        <v>71</v>
-      </c>
       <c r="R2" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="S2" s="22" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T2" s="18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="U2" s="19">
-        <f t="shared" ref="U2:U3" ca="1" si="1">L2</f>
+        <f t="shared" ref="U2:U3" si="1">L2</f>
         <v>45761</v>
       </c>
       <c r="V2" s="18" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W2" s="23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="X2" s="21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Y2" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Z2" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AA2" s="25" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AB2" s="14">
         <v>40</v>
       </c>
       <c r="AC2" s="26" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AD2" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AE2" s="19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AF2" s="18" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AG2" s="27" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AH2" s="18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI2" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ2" s="28" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AK2" s="18">
         <v>99</v>
       </c>
       <c r="AL2" s="21">
-        <f t="shared" ref="AL2:AL3" ca="1" si="2">TODAY()+60</f>
+        <f t="shared" ref="AL2:AL3" si="2">TODAY()+60</f>
         <v>45852</v>
       </c>
       <c r="AM2" s="21">
-        <f t="shared" ref="AM2:AM3" ca="1" si="3">U2</f>
+        <f t="shared" ref="AM2:AM3" si="3">U2</f>
         <v>45761</v>
       </c>
       <c r="AN2" s="29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AO2" s="20" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AP2" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="AQ2" s="19" t="str">
+        <v>95</v>
+      </c>
+      <c r="AQ2" s="19">
         <f t="shared" ref="AQ2:AQ3" si="4">AE2</f>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AR2" s="14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS2" s="14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AT2" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="AU2" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="AU2" s="14" t="s">
-        <v>94</v>
-      </c>
       <c r="AV2" s="30" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AW2" s="21" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AX2" s="30" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AY2" s="30" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AZ2" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="BA2" s="31" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BB2" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BC2" s="31" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BD2" s="32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BE2" s="32" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BF2" s="33">
         <v>10000895673</v>
       </c>
       <c r="BG2" s="32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BH2" s="32" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BI2" s="33">
         <v>100845873</v>
       </c>
       <c r="BJ2" s="32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BK2" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BL2" s="35" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="BM2" s="32" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BN2" s="32" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BO2" s="32" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BP2" s="12"/>
       <c r="BQ2" s="12"/>
@@ -1476,208 +1459,212 @@
       <c r="BX2" s="12"/>
       <c r="BY2" s="12"/>
     </row>
-    <row r="3" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
+        <v>111</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>66</v>
+      </c>
       <c r="D3" s="13" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I3" s="18">
         <v>234456532</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L3" s="19">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45761</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N3" s="20" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O3" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="P3" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q3" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="P3" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q3" s="18" t="s">
-        <v>71</v>
-      </c>
       <c r="R3" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="S3" s="22" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T3" s="18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="U3" s="19">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45761</v>
       </c>
       <c r="V3" s="18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="W3" s="23" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="X3" s="21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Y3" s="24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="Z3" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AA3" s="25" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AB3" s="14">
         <v>40</v>
       </c>
       <c r="AC3" s="26" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AD3" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AE3" s="19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AF3" s="18" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AG3" s="37">
         <v>251</v>
       </c>
       <c r="AH3" s="18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI3" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ3" s="28" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AK3" s="18">
         <v>99</v>
       </c>
       <c r="AL3" s="21">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45852</v>
       </c>
       <c r="AM3" s="21">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>45761</v>
       </c>
       <c r="AN3" s="29" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AO3" s="20" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AP3" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="AQ3" s="19" t="str">
+        <v>95</v>
+      </c>
+      <c r="AQ3" s="19">
         <f t="shared" si="4"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AR3" s="14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AS3" s="14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AT3" s="14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AU3" s="14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AV3" s="30" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AW3" s="21" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AX3" s="30" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AY3" s="30" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AZ3" s="30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="BA3" s="31" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="BB3" s="21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="BC3" s="31" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BD3" s="32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BE3" s="32" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BF3" s="33">
         <v>10000895671</v>
       </c>
       <c r="BG3" s="32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BH3" s="32" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="BI3" s="33">
         <v>100845871</v>
       </c>
       <c r="BJ3" s="32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="BK3" s="34" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="BL3" s="35" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="BM3" s="32" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BN3" s="32" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BO3" s="32" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BP3" s="12"/>
       <c r="BQ3" s="12"/>
@@ -1690,7 +1677,7 @@
       <c r="BX3" s="12"/>
       <c r="BY3" s="12"/>
     </row>
-    <row r="4" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="36"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -1769,7 +1756,7 @@
       <c r="BX4" s="12"/>
       <c r="BY4" s="12"/>
     </row>
-    <row r="5" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="36"/>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
@@ -1848,7 +1835,7 @@
       <c r="BX5" s="12"/>
       <c r="BY5" s="12"/>
     </row>
-    <row r="6" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="36"/>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -1926,7 +1913,7 @@
       <c r="BX6" s="12"/>
       <c r="BY6" s="12"/>
     </row>
-    <row r="7" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="36"/>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -2005,7 +1992,7 @@
       <c r="BX7" s="12"/>
       <c r="BY7" s="12"/>
     </row>
-    <row r="8" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="36"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -2084,7 +2071,7 @@
       <c r="BX8" s="12"/>
       <c r="BY8" s="12"/>
     </row>
-    <row r="9" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="36"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -2163,7 +2150,7 @@
       <c r="BX9" s="12"/>
       <c r="BY9" s="12"/>
     </row>
-    <row r="10" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="36"/>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -2242,7 +2229,7 @@
       <c r="BX10" s="12"/>
       <c r="BY10" s="12"/>
     </row>
-    <row r="11" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="36"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -2321,7 +2308,7 @@
       <c r="BX11" s="12"/>
       <c r="BY11" s="12"/>
     </row>
-    <row r="12" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="36"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -2400,7 +2387,7 @@
       <c r="BX12" s="12"/>
       <c r="BY12" s="12"/>
     </row>
-    <row r="13" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="36"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -2479,7 +2466,7 @@
       <c r="BX13" s="12"/>
       <c r="BY13" s="12"/>
     </row>
-    <row r="14" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="36"/>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -2558,7 +2545,7 @@
       <c r="BX14" s="12"/>
       <c r="BY14" s="12"/>
     </row>
-    <row r="15" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="36"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -2637,7 +2624,7 @@
       <c r="BX15" s="12"/>
       <c r="BY15" s="12"/>
     </row>
-    <row r="16" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="36"/>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
@@ -2716,7 +2703,7 @@
       <c r="BX16" s="12"/>
       <c r="BY16" s="12"/>
     </row>
-    <row r="17" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -2796,7 +2783,7 @@
       <c r="BY17" s="12"/>
       <c r="BZ17" s="12"/>
     </row>
-    <row r="18" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
@@ -2876,7 +2863,7 @@
       <c r="BY18" s="12"/>
       <c r="BZ18" s="12"/>
     </row>
-    <row r="19" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
@@ -2956,7 +2943,7 @@
       <c r="BY19" s="12"/>
       <c r="BZ19" s="12"/>
     </row>
-    <row r="20" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -3036,7 +3023,7 @@
       <c r="BY20" s="12"/>
       <c r="BZ20" s="12"/>
     </row>
-    <row r="21" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -3116,7 +3103,7 @@
       <c r="BY21" s="12"/>
       <c r="BZ21" s="12"/>
     </row>
-    <row r="22" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -3196,7 +3183,7 @@
       <c r="BY22" s="12"/>
       <c r="BZ22" s="12"/>
     </row>
-    <row r="23" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -3276,7 +3263,7 @@
       <c r="BY23" s="12"/>
       <c r="BZ23" s="12"/>
     </row>
-    <row r="24" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -3356,7 +3343,7 @@
       <c r="BY24" s="12"/>
       <c r="BZ24" s="12"/>
     </row>
-    <row r="25" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -3436,7 +3423,7 @@
       <c r="BY25" s="12"/>
       <c r="BZ25" s="12"/>
     </row>
-    <row r="26" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -3516,7 +3503,7 @@
       <c r="BY26" s="12"/>
       <c r="BZ26" s="12"/>
     </row>
-    <row r="27" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
@@ -3596,7 +3583,7 @@
       <c r="BY27" s="12"/>
       <c r="BZ27" s="12"/>
     </row>
-    <row r="28" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
@@ -3676,7 +3663,7 @@
       <c r="BY28" s="12"/>
       <c r="BZ28" s="12"/>
     </row>
-    <row r="29" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -3756,7 +3743,7 @@
       <c r="BY29" s="12"/>
       <c r="BZ29" s="12"/>
     </row>
-    <row r="30" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -3836,7 +3823,7 @@
       <c r="BY30" s="12"/>
       <c r="BZ30" s="12"/>
     </row>
-    <row r="31" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
@@ -3916,7 +3903,7 @@
       <c r="BY31" s="12"/>
       <c r="BZ31" s="12"/>
     </row>
-    <row r="32" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
@@ -3996,7 +3983,7 @@
       <c r="BY32" s="12"/>
       <c r="BZ32" s="12"/>
     </row>
-    <row r="33" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -4076,7 +4063,7 @@
       <c r="BY33" s="12"/>
       <c r="BZ33" s="12"/>
     </row>
-    <row r="34" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
@@ -4156,7 +4143,7 @@
       <c r="BY34" s="12"/>
       <c r="BZ34" s="12"/>
     </row>
-    <row r="35" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
@@ -4236,7 +4223,7 @@
       <c r="BY35" s="12"/>
       <c r="BZ35" s="12"/>
     </row>
-    <row r="36" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -4316,7 +4303,7 @@
       <c r="BY36" s="12"/>
       <c r="BZ36" s="12"/>
     </row>
-    <row r="37" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
@@ -4396,7 +4383,7 @@
       <c r="BY37" s="12"/>
       <c r="BZ37" s="12"/>
     </row>
-    <row r="38" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
@@ -4476,7 +4463,7 @@
       <c r="BY38" s="12"/>
       <c r="BZ38" s="12"/>
     </row>
-    <row r="39" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
@@ -4556,7 +4543,7 @@
       <c r="BY39" s="12"/>
       <c r="BZ39" s="12"/>
     </row>
-    <row r="40" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -4636,7 +4623,7 @@
       <c r="BY40" s="12"/>
       <c r="BZ40" s="12"/>
     </row>
-    <row r="41" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="41" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
@@ -4716,7 +4703,7 @@
       <c r="BY41" s="12"/>
       <c r="BZ41" s="12"/>
     </row>
-    <row r="42" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="42" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
@@ -4796,7 +4783,7 @@
       <c r="BY42" s="12"/>
       <c r="BZ42" s="12"/>
     </row>
-    <row r="43" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="43" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
@@ -4876,7 +4863,7 @@
       <c r="BY43" s="12"/>
       <c r="BZ43" s="12"/>
     </row>
-    <row r="44" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="44" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12"/>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
@@ -4956,7 +4943,7 @@
       <c r="BY44" s="12"/>
       <c r="BZ44" s="12"/>
     </row>
-    <row r="45" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="45" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
@@ -5036,7 +5023,7 @@
       <c r="BY45" s="12"/>
       <c r="BZ45" s="12"/>
     </row>
-    <row r="46" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="46" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12"/>
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
@@ -5116,7 +5103,7 @@
       <c r="BY46" s="12"/>
       <c r="BZ46" s="12"/>
     </row>
-    <row r="47" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="47" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12"/>
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
@@ -5196,7 +5183,7 @@
       <c r="BY47" s="12"/>
       <c r="BZ47" s="12"/>
     </row>
-    <row r="48" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="48" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12"/>
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
@@ -5276,7 +5263,7 @@
       <c r="BY48" s="12"/>
       <c r="BZ48" s="12"/>
     </row>
-    <row r="49" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="49" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12"/>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
@@ -5356,7 +5343,7 @@
       <c r="BY49" s="12"/>
       <c r="BZ49" s="12"/>
     </row>
-    <row r="50" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="50" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12"/>
       <c r="B50" s="12"/>
       <c r="C50" s="12"/>
@@ -5436,7 +5423,7 @@
       <c r="BY50" s="12"/>
       <c r="BZ50" s="12"/>
     </row>
-    <row r="51" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="12"/>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
@@ -5516,7 +5503,7 @@
       <c r="BY51" s="12"/>
       <c r="BZ51" s="12"/>
     </row>
-    <row r="52" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="52" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="12"/>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
@@ -5596,7 +5583,7 @@
       <c r="BY52" s="12"/>
       <c r="BZ52" s="12"/>
     </row>
-    <row r="53" spans="1:78" s="10" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="12"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -5676,7 +5663,7 @@
       <c r="BY53" s="12"/>
       <c r="BZ53" s="12"/>
     </row>
-    <row r="54" spans="1:78" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="54" ht="14.5" customHeight="1" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A54" s="12"/>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
@@ -5756,78 +5743,78 @@
       <c r="BY54" s="12"/>
       <c r="BZ54" s="12"/>
     </row>
-    <row r="55" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F55" s="12"/>
     </row>
-    <row r="56" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F56" s="12"/>
     </row>
-    <row r="57" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F57" s="12"/>
     </row>
-    <row r="58" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F58" s="12"/>
     </row>
-    <row r="59" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F59" s="12"/>
     </row>
-    <row r="60" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F60" s="12"/>
     </row>
-    <row r="61" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F61" s="12"/>
     </row>
-    <row r="62" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F62" s="12"/>
     </row>
-    <row r="63" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F63" s="12"/>
     </row>
-    <row r="64" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F64" s="12"/>
     </row>
-    <row r="65" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F65" s="12"/>
     </row>
-    <row r="66" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F66" s="12"/>
     </row>
-    <row r="67" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F67" s="12"/>
     </row>
-    <row r="68" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F68" s="12"/>
     </row>
-    <row r="69" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F69" s="12"/>
     </row>
-    <row r="70" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F70" s="12"/>
     </row>
-    <row r="71" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F71" s="12"/>
     </row>
-    <row r="72" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F72" s="12"/>
     </row>
-    <row r="73" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F73" s="12"/>
     </row>
-    <row r="74" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F74" s="12"/>
     </row>
-    <row r="75" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F75" s="12"/>
     </row>
-    <row r="76" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F76" s="12"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="S3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="S2" r:id="rId1"/>
+    <hyperlink ref="S3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_Portugal_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Portugal_Regression_PK17.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="125">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -214,7 +214,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10698964</t>
+    <t>10699017</t>
   </si>
   <si>
     <t>Passed</t>
@@ -226,10 +226,10 @@
     <t>Portugal</t>
   </si>
   <si>
-    <t>PortugalNmg</t>
-  </si>
-  <si>
-    <t>DryRunTesting1</t>
+    <t>Kyler</t>
+  </si>
+  <si>
+    <t>Abernathy</t>
   </si>
   <si>
     <t>Sr.</t>
@@ -340,7 +340,7 @@
     <t>ID Number (Numero de</t>
   </si>
   <si>
-    <t>24982928 2AP35</t>
+    <t>24982928 2AP43</t>
   </si>
   <si>
     <t>BBVAESMM128</t>
@@ -355,13 +355,16 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10698966</t>
+    <t>10699025</t>
   </si>
   <si>
     <t>420 Store Management (Rilyv Zisozy (4206015))</t>
   </si>
   <si>
-    <t>PortugalMg</t>
+    <t>Harry</t>
+  </si>
+  <si>
+    <t>Herzog</t>
   </si>
   <si>
     <t>Sra.</t>
@@ -370,7 +373,7 @@
     <t>New</t>
   </si>
   <si>
-    <t>Auto 65359157</t>
+    <t>Auto 90099085</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -388,7 +391,7 @@
     <t>Single</t>
   </si>
   <si>
-    <t>24982928 2AP36</t>
+    <t>24982928 2AP45</t>
   </si>
 </sst>
 </file>
@@ -1271,7 +1274,7 @@
       </c>
       <c r="L2" s="19">
         <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45754</v>
+        <v>45755</v>
       </c>
       <c r="M2" s="14" t="s">
         <v>68</v>
@@ -1299,7 +1302,7 @@
       </c>
       <c r="U2" s="19">
         <f t="shared" ref="U2:U3" si="1">L2</f>
-        <v>45754</v>
+        <v>45755</v>
       </c>
       <c r="V2" s="18" t="s">
         <v>79</v>
@@ -1351,11 +1354,11 @@
       </c>
       <c r="AL2" s="21">
         <f t="shared" ref="AL2:AL3" si="2">TODAY()+60</f>
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="AM2" s="21">
         <f t="shared" ref="AM2:AM3" si="3">U2</f>
-        <v>45754</v>
+        <v>45755</v>
       </c>
       <c r="AN2" s="29" t="s">
         <v>93</v>
@@ -1413,7 +1416,7 @@
         <v>104</v>
       </c>
       <c r="BF2" s="33">
-        <v>10000895681</v>
+        <v>10000895673</v>
       </c>
       <c r="BG2" s="32" t="s">
         <v>68</v>
@@ -1422,7 +1425,7 @@
         <v>105</v>
       </c>
       <c r="BI2" s="33">
-        <v>100845881</v>
+        <v>100845873</v>
       </c>
       <c r="BJ2" s="32" t="s">
         <v>68</v>
@@ -1473,10 +1476,10 @@
         <v>114</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I3" s="18">
         <v>234456532</v>
@@ -1489,7 +1492,7 @@
       </c>
       <c r="L3" s="19">
         <f t="shared" si="0"/>
-        <v>45754</v>
+        <v>45755</v>
       </c>
       <c r="M3" s="14" t="s">
         <v>68</v>
@@ -1517,19 +1520,19 @@
       </c>
       <c r="U3" s="19">
         <f t="shared" si="1"/>
-        <v>45754</v>
+        <v>45755</v>
       </c>
       <c r="V3" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="W3" s="23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="X3" s="21" t="s">
         <v>81</v>
       </c>
       <c r="Y3" s="24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Z3" s="21" t="s">
         <v>83</v>
@@ -1550,7 +1553,7 @@
         <v>87</v>
       </c>
       <c r="AF3" s="18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG3" s="37">
         <v>251</v>
@@ -1569,14 +1572,14 @@
       </c>
       <c r="AL3" s="21">
         <f t="shared" si="2"/>
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="AM3" s="21">
         <f t="shared" si="3"/>
-        <v>45754</v>
+        <v>45755</v>
       </c>
       <c r="AN3" s="29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AO3" s="20" t="s">
         <v>94</v>
@@ -1601,7 +1604,7 @@
         <v>96</v>
       </c>
       <c r="AV3" s="30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AW3" s="21" t="s">
         <v>100</v>
@@ -1616,7 +1619,7 @@
         <v>76</v>
       </c>
       <c r="BA3" s="31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BB3" s="21" t="s">
         <v>87</v>
@@ -1631,7 +1634,7 @@
         <v>104</v>
       </c>
       <c r="BF3" s="33">
-        <v>10000895680</v>
+        <v>10000895671</v>
       </c>
       <c r="BG3" s="32" t="s">
         <v>68</v>
@@ -1640,7 +1643,7 @@
         <v>105</v>
       </c>
       <c r="BI3" s="33">
-        <v>100845880</v>
+        <v>100845871</v>
       </c>
       <c r="BJ3" s="32" t="s">
         <v>68</v>
@@ -1649,7 +1652,7 @@
         <v>106</v>
       </c>
       <c r="BL3" s="35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BM3" s="32" t="s">
         <v>108</v>

--- a/Data/Hires/Workday_NewHire_Portugal_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Portugal_Regression_PK17.xlsx
@@ -214,7 +214,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699529</t>
+    <t>10699619</t>
   </si>
   <si>
     <t>Passed</t>
@@ -226,10 +226,10 @@
     <t>Portugal</t>
   </si>
   <si>
-    <t>Evelyn</t>
-  </si>
-  <si>
-    <t>Grimes</t>
+    <t>Rhett</t>
+  </si>
+  <si>
+    <t>Bernier</t>
   </si>
   <si>
     <t>Sr.</t>
@@ -340,7 +340,7 @@
     <t>ID Number (Numero de</t>
   </si>
   <si>
-    <t>24982928 2AP55</t>
+    <t>24982928 2AP70</t>
   </si>
   <si>
     <t>BBVAESMM128</t>
@@ -355,16 +355,16 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10699530</t>
+    <t>10699620</t>
   </si>
   <si>
     <t>420 Store Management (Rilyv Zisozy (4206015))</t>
   </si>
   <si>
-    <t>Nathanael</t>
-  </si>
-  <si>
-    <t>Waters-Mann</t>
+    <t>Muriel</t>
+  </si>
+  <si>
+    <t>Little</t>
   </si>
   <si>
     <t>Sra.</t>
@@ -373,7 +373,7 @@
     <t>New</t>
   </si>
   <si>
-    <t>Auto 79934795</t>
+    <t>Auto 22222544</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -391,7 +391,7 @@
     <t>Single</t>
   </si>
   <si>
-    <t>24982928 2AP56</t>
+    <t>24982928 2AP71</t>
   </si>
 </sst>
 </file>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="L2" s="20">
         <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="M2" s="15" t="s">
         <v>68</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="U2" s="20">
         <f t="shared" ref="U2:U3" si="1">L2</f>
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="V2" s="19" t="s">
         <v>79</v>
@@ -1357,11 +1357,11 @@
       </c>
       <c r="AL2" s="22">
         <f t="shared" ref="AL2:AL3" si="2">TODAY()+60</f>
-        <v>45870</v>
+        <v>45877</v>
       </c>
       <c r="AM2" s="22">
         <f t="shared" ref="AM2:AM3" si="3">U2</f>
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="AN2" s="30" t="s">
         <v>93</v>
@@ -1419,7 +1419,7 @@
         <v>104</v>
       </c>
       <c r="BF2" s="34">
-        <v>10000895708</v>
+        <v>10000895720</v>
       </c>
       <c r="BG2" s="33" t="s">
         <v>68</v>
@@ -1428,7 +1428,7 @@
         <v>105</v>
       </c>
       <c r="BI2" s="34">
-        <v>100845907</v>
+        <v>100845911</v>
       </c>
       <c r="BJ2" s="33" t="s">
         <v>68</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="L3" s="20">
         <f t="shared" si="0"/>
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>68</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="U3" s="20">
         <f t="shared" si="1"/>
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="V3" s="19" t="s">
         <v>117</v>
@@ -1575,11 +1575,11 @@
       </c>
       <c r="AL3" s="22">
         <f t="shared" si="2"/>
-        <v>45870</v>
+        <v>45877</v>
       </c>
       <c r="AM3" s="22">
         <f t="shared" si="3"/>
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="AN3" s="30" t="s">
         <v>121</v>
@@ -1637,7 +1637,7 @@
         <v>104</v>
       </c>
       <c r="BF3" s="34">
-        <v>10000895709</v>
+        <v>10000895721</v>
       </c>
       <c r="BG3" s="33" t="s">
         <v>68</v>
@@ -1646,7 +1646,7 @@
         <v>105</v>
       </c>
       <c r="BI3" s="34">
-        <v>100845908</v>
+        <v>100845912</v>
       </c>
       <c r="BJ3" s="33" t="s">
         <v>68</v>

--- a/Data/Hires/Workday_NewHire_Portugal_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Portugal_Regression_PK17.xlsx
@@ -1,18 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{18EA4F93-B1EE-4025-A276-3650BF31B9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BY$53</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -397,92 +412,92 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color indexed="12"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="7"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
       <family val="3"/>
-      <sz val="7"/>
-      <name val="Courier New"/>
     </font>
     <font>
+      <sz val="10"/>
       <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -505,7 +520,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -522,7 +537,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,24 +557,42 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -956,9 +989,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BZ76"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.36328125" customWidth="1"/>
     <col min="2" max="2" width="72.6328125" customWidth="1"/>
@@ -1038,7 +1071,7 @@
     <col min="77" max="77" width="22.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.4" customHeight="1" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:77" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1241,7 +1274,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>64</v>
       </c>
@@ -1276,8 +1309,8 @@
         <v>73</v>
       </c>
       <c r="L2" s="20">
-        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45796</v>
+        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
+        <v>45829</v>
       </c>
       <c r="M2" s="15" t="s">
         <v>68</v>
@@ -1304,8 +1337,8 @@
         <v>73</v>
       </c>
       <c r="U2" s="20">
-        <f t="shared" ref="U2:U3" si="1">L2</f>
-        <v>45796</v>
+        <f t="shared" ref="U2:U3" ca="1" si="1">L2</f>
+        <v>45829</v>
       </c>
       <c r="V2" s="19" t="s">
         <v>79</v>
@@ -1356,12 +1389,12 @@
         <v>99</v>
       </c>
       <c r="AL2" s="22">
-        <f t="shared" ref="AL2:AL3" si="2">TODAY()+60</f>
-        <v>45887</v>
+        <f t="shared" ref="AL2:AL3" ca="1" si="2">TODAY()+60</f>
+        <v>45920</v>
       </c>
       <c r="AM2" s="22">
-        <f t="shared" ref="AM2:AM3" si="3">U2</f>
-        <v>45796</v>
+        <f t="shared" ref="AM2:AM3" ca="1" si="3">U2</f>
+        <v>45829</v>
       </c>
       <c r="AN2" s="30" t="s">
         <v>93</v>
@@ -1372,9 +1405,9 @@
       <c r="AP2" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="AQ2" s="20">
+      <c r="AQ2" s="20" t="str">
         <f t="shared" ref="AQ2:AQ3" si="4">AE2</f>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AR2" s="15" t="s">
         <v>96</v>
@@ -1459,7 +1492,7 @@
       <c r="BX2" s="13"/>
       <c r="BY2" s="13"/>
     </row>
-    <row r="3" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="37" t="s">
         <v>111</v>
       </c>
@@ -1494,8 +1527,8 @@
         <v>73</v>
       </c>
       <c r="L3" s="20">
-        <f t="shared" si="0"/>
-        <v>45796</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45829</v>
       </c>
       <c r="M3" s="15" t="s">
         <v>68</v>
@@ -1522,8 +1555,8 @@
         <v>73</v>
       </c>
       <c r="U3" s="20">
-        <f t="shared" si="1"/>
-        <v>45796</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>45829</v>
       </c>
       <c r="V3" s="19" t="s">
         <v>117</v>
@@ -1574,12 +1607,12 @@
         <v>99</v>
       </c>
       <c r="AL3" s="22">
-        <f t="shared" si="2"/>
-        <v>45887</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45920</v>
       </c>
       <c r="AM3" s="22">
-        <f t="shared" si="3"/>
-        <v>45796</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>45829</v>
       </c>
       <c r="AN3" s="30" t="s">
         <v>121</v>
@@ -1590,9 +1623,9 @@
       <c r="AP3" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="AQ3" s="20">
+      <c r="AQ3" s="20" t="str">
         <f t="shared" si="4"/>
-        <v>NaN</v>
+        <v>N/A</v>
       </c>
       <c r="AR3" s="15" t="s">
         <v>96</v>
@@ -1677,7 +1710,7 @@
       <c r="BX3" s="13"/>
       <c r="BY3" s="13"/>
     </row>
-    <row r="4" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1756,7 +1789,7 @@
       <c r="BX4" s="13"/>
       <c r="BY4" s="13"/>
     </row>
-    <row r="5" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37"/>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -1835,7 +1868,7 @@
       <c r="BX5" s="13"/>
       <c r="BY5" s="13"/>
     </row>
-    <row r="6" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="37"/>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -1913,7 +1946,7 @@
       <c r="BX6" s="13"/>
       <c r="BY6" s="13"/>
     </row>
-    <row r="7" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="37"/>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -1992,7 +2025,7 @@
       <c r="BX7" s="13"/>
       <c r="BY7" s="13"/>
     </row>
-    <row r="8" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="37"/>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -2071,7 +2104,7 @@
       <c r="BX8" s="13"/>
       <c r="BY8" s="13"/>
     </row>
-    <row r="9" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="37"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -2150,7 +2183,7 @@
       <c r="BX9" s="13"/>
       <c r="BY9" s="13"/>
     </row>
-    <row r="10" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="37"/>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -2229,7 +2262,7 @@
       <c r="BX10" s="13"/>
       <c r="BY10" s="13"/>
     </row>
-    <row r="11" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="37"/>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -2308,7 +2341,7 @@
       <c r="BX11" s="13"/>
       <c r="BY11" s="13"/>
     </row>
-    <row r="12" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37"/>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -2387,7 +2420,7 @@
       <c r="BX12" s="13"/>
       <c r="BY12" s="13"/>
     </row>
-    <row r="13" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2466,7 +2499,7 @@
       <c r="BX13" s="13"/>
       <c r="BY13" s="13"/>
     </row>
-    <row r="14" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="37"/>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -2545,7 +2578,7 @@
       <c r="BX14" s="13"/>
       <c r="BY14" s="13"/>
     </row>
-    <row r="15" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="37"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2624,7 +2657,7 @@
       <c r="BX15" s="13"/>
       <c r="BY15" s="13"/>
     </row>
-    <row r="16" ht="17.4" customHeight="1" spans="1:77" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:77" s="10" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="37"/>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -2703,7 +2736,7 @@
       <c r="BX16" s="13"/>
       <c r="BY16" s="13"/>
     </row>
-    <row r="17" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -2783,7 +2816,7 @@
       <c r="BY17" s="13"/>
       <c r="BZ17" s="13"/>
     </row>
-    <row r="18" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="13"/>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -2863,7 +2896,7 @@
       <c r="BY18" s="13"/>
       <c r="BZ18" s="13"/>
     </row>
-    <row r="19" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="13"/>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -2943,7 +2976,7 @@
       <c r="BY19" s="13"/>
       <c r="BZ19" s="13"/>
     </row>
-    <row r="20" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -3023,7 +3056,7 @@
       <c r="BY20" s="13"/>
       <c r="BZ20" s="13"/>
     </row>
-    <row r="21" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="13"/>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -3103,7 +3136,7 @@
       <c r="BY21" s="13"/>
       <c r="BZ21" s="13"/>
     </row>
-    <row r="22" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="13"/>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
@@ -3183,7 +3216,7 @@
       <c r="BY22" s="13"/>
       <c r="BZ22" s="13"/>
     </row>
-    <row r="23" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="13"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3263,7 +3296,7 @@
       <c r="BY23" s="13"/>
       <c r="BZ23" s="13"/>
     </row>
-    <row r="24" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="13"/>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -3343,7 +3376,7 @@
       <c r="BY24" s="13"/>
       <c r="BZ24" s="13"/>
     </row>
-    <row r="25" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="13"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -3423,7 +3456,7 @@
       <c r="BY25" s="13"/>
       <c r="BZ25" s="13"/>
     </row>
-    <row r="26" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="13"/>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
@@ -3503,7 +3536,7 @@
       <c r="BY26" s="13"/>
       <c r="BZ26" s="13"/>
     </row>
-    <row r="27" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="13"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -3583,7 +3616,7 @@
       <c r="BY27" s="13"/>
       <c r="BZ27" s="13"/>
     </row>
-    <row r="28" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="13"/>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -3663,7 +3696,7 @@
       <c r="BY28" s="13"/>
       <c r="BZ28" s="13"/>
     </row>
-    <row r="29" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="13"/>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -3743,7 +3776,7 @@
       <c r="BY29" s="13"/>
       <c r="BZ29" s="13"/>
     </row>
-    <row r="30" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="13"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -3823,7 +3856,7 @@
       <c r="BY30" s="13"/>
       <c r="BZ30" s="13"/>
     </row>
-    <row r="31" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -3903,7 +3936,7 @@
       <c r="BY31" s="13"/>
       <c r="BZ31" s="13"/>
     </row>
-    <row r="32" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="13"/>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
@@ -3983,7 +4016,7 @@
       <c r="BY32" s="13"/>
       <c r="BZ32" s="13"/>
     </row>
-    <row r="33" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="13"/>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -4063,7 +4096,7 @@
       <c r="BY33" s="13"/>
       <c r="BZ33" s="13"/>
     </row>
-    <row r="34" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="13"/>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -4143,7 +4176,7 @@
       <c r="BY34" s="13"/>
       <c r="BZ34" s="13"/>
     </row>
-    <row r="35" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="13"/>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -4223,7 +4256,7 @@
       <c r="BY35" s="13"/>
       <c r="BZ35" s="13"/>
     </row>
-    <row r="36" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="13"/>
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
@@ -4303,7 +4336,7 @@
       <c r="BY36" s="13"/>
       <c r="BZ36" s="13"/>
     </row>
-    <row r="37" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="13"/>
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
@@ -4383,7 +4416,7 @@
       <c r="BY37" s="13"/>
       <c r="BZ37" s="13"/>
     </row>
-    <row r="38" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="13"/>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
@@ -4463,7 +4496,7 @@
       <c r="BY38" s="13"/>
       <c r="BZ38" s="13"/>
     </row>
-    <row r="39" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="13"/>
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
@@ -4543,7 +4576,7 @@
       <c r="BY39" s="13"/>
       <c r="BZ39" s="13"/>
     </row>
-    <row r="40" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="13"/>
       <c r="B40" s="13"/>
       <c r="C40" s="13"/>
@@ -4623,7 +4656,7 @@
       <c r="BY40" s="13"/>
       <c r="BZ40" s="13"/>
     </row>
-    <row r="41" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="13"/>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
@@ -4703,7 +4736,7 @@
       <c r="BY41" s="13"/>
       <c r="BZ41" s="13"/>
     </row>
-    <row r="42" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="13"/>
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
@@ -4783,7 +4816,7 @@
       <c r="BY42" s="13"/>
       <c r="BZ42" s="13"/>
     </row>
-    <row r="43" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="13"/>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -4863,7 +4896,7 @@
       <c r="BY43" s="13"/>
       <c r="BZ43" s="13"/>
     </row>
-    <row r="44" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
@@ -4943,7 +4976,7 @@
       <c r="BY44" s="13"/>
       <c r="BZ44" s="13"/>
     </row>
-    <row r="45" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="13"/>
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
@@ -5023,7 +5056,7 @@
       <c r="BY45" s="13"/>
       <c r="BZ45" s="13"/>
     </row>
-    <row r="46" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="13"/>
       <c r="B46" s="13"/>
       <c r="C46" s="13"/>
@@ -5103,7 +5136,7 @@
       <c r="BY46" s="13"/>
       <c r="BZ46" s="13"/>
     </row>
-    <row r="47" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="13"/>
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
@@ -5183,7 +5216,7 @@
       <c r="BY47" s="13"/>
       <c r="BZ47" s="13"/>
     </row>
-    <row r="48" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="13"/>
       <c r="B48" s="13"/>
       <c r="C48" s="13"/>
@@ -5263,7 +5296,7 @@
       <c r="BY48" s="13"/>
       <c r="BZ48" s="13"/>
     </row>
-    <row r="49" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="13"/>
       <c r="B49" s="13"/>
       <c r="C49" s="13"/>
@@ -5343,7 +5376,7 @@
       <c r="BY49" s="13"/>
       <c r="BZ49" s="13"/>
     </row>
-    <row r="50" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="13"/>
       <c r="B50" s="13"/>
       <c r="C50" s="13"/>
@@ -5423,7 +5456,7 @@
       <c r="BY50" s="13"/>
       <c r="BZ50" s="13"/>
     </row>
-    <row r="51" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="13"/>
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
@@ -5503,7 +5536,7 @@
       <c r="BY51" s="13"/>
       <c r="BZ51" s="13"/>
     </row>
-    <row r="52" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="13"/>
       <c r="B52" s="13"/>
       <c r="C52" s="13"/>
@@ -5583,7 +5616,7 @@
       <c r="BY52" s="13"/>
       <c r="BZ52" s="13"/>
     </row>
-    <row r="53" ht="14.5" customHeight="1" spans="1:78" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:78" s="10" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="13"/>
       <c r="B53" s="13"/>
       <c r="C53" s="13"/>
@@ -5663,7 +5696,7 @@
       <c r="BY53" s="13"/>
       <c r="BZ53" s="13"/>
     </row>
-    <row r="54" ht="14.5" customHeight="1" spans="1:78" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:78" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="13"/>
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
@@ -5743,78 +5776,78 @@
       <c r="BY54" s="13"/>
       <c r="BZ54" s="13"/>
     </row>
-    <row r="55" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F55" s="13"/>
     </row>
-    <row r="56" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F56" s="13"/>
     </row>
-    <row r="57" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F57" s="13"/>
     </row>
-    <row r="58" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F58" s="13"/>
     </row>
-    <row r="59" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F59" s="13"/>
     </row>
-    <row r="60" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F60" s="13"/>
     </row>
-    <row r="61" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F61" s="13"/>
     </row>
-    <row r="62" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F62" s="13"/>
     </row>
-    <row r="63" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F63" s="13"/>
     </row>
-    <row r="64" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:78" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F64" s="13"/>
     </row>
-    <row r="65" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F65" s="13"/>
     </row>
-    <row r="66" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F66" s="13"/>
     </row>
-    <row r="67" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F67" s="13"/>
     </row>
-    <row r="68" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F68" s="13"/>
     </row>
-    <row r="69" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F69" s="13"/>
     </row>
-    <row r="70" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F70" s="13"/>
     </row>
-    <row r="71" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F71" s="13"/>
     </row>
-    <row r="72" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F72" s="13"/>
     </row>
-    <row r="73" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F73" s="13"/>
     </row>
-    <row r="74" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F74" s="13"/>
     </row>
-    <row r="75" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F75" s="13"/>
     </row>
-    <row r="76" ht="14.4" customHeight="1" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="6:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F76" s="13"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S2" r:id="rId1"/>
-    <hyperlink ref="S3" r:id="rId2"/>
+    <hyperlink ref="S2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="S3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_Portugal_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Portugal_Regression_PK17.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="124">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -214,10 +214,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10700256</t>
-  </si>
-  <si>
-    <t>Test failed for 'Houston Stark' Employee: Errors and AlertsErrorsAlertsNational IDs (Row 1)This national identifier you entered is already in use. Verify that the information is accurate.National IDs (Row 2)This national identifier you entered is already in use. Verify that the information is accurate.National IDs (Row 3)This national identifier you entered is already in use. Verify that the information is accurate. &amp; find failed Screenshot Path:-&gt;H:\Clone-Workday-Playwright/WorkdayFailedScreenshot/2025-07-15T11-43-25-344Z.png</t>
+    <t>Test failed for 'Dorthy Deckow' Employee: Errors and AlertsErrorsAlertsNational IDs (Row 1)This national identifier you entered is already in use. Verify that the information is accurate.National IDs (Row 2)This national identifier you entered is already in use. Verify that the information is accurate.National IDs (Row 3)This national identifier you entered is already in use. Verify that the information is accurate. &amp; find failed Screenshot Path:-&gt;H:\Clone-Workday-Playwright/WorkdayFailedScreenshot/2025-08-05T06-55-42-184Z.png</t>
   </si>
   <si>
     <t>420 Recruitment (Gozyb Sosobo (10034456))</t>
@@ -226,10 +223,10 @@
     <t>Portugal</t>
   </si>
   <si>
-    <t>Houston</t>
-  </si>
-  <si>
-    <t>Stark</t>
+    <t>Dorthy</t>
+  </si>
+  <si>
+    <t>Deckow</t>
   </si>
   <si>
     <t>Sr.</t>
@@ -340,7 +337,7 @@
     <t>ID Number (Numero de</t>
   </si>
   <si>
-    <t>24983028 3AP06</t>
+    <t>24983028 3AP24</t>
   </si>
   <si>
     <t>BBVAESMM128</t>
@@ -355,19 +352,16 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10700257</t>
-  </si>
-  <si>
-    <t>Test failed for 'Priscilla Harris' Employee: Errors and AlertsErrorsAlertsNational IDs (Row 1)This national identifier you entered is already in use. Verify that the information is accurate.National IDs (Row 2)This national identifier you entered is already in use. Verify that the information is accurate.National IDs (Row 3)This national identifier you entered is already in use. Verify that the information is accurate. &amp; find failed Screenshot Path:-&gt;H:\Clone-Workday-Playwright/WorkdayFailedScreenshot/2025-07-15T11-50-17-368Z.png</t>
+    <t>Test failed for 'Itzel Grant' Employee: Errors and AlertsErrorsAlertsNational IDs (Row 1)This national identifier you entered is already in use. Verify that the information is accurate.National IDs (Row 2)This national identifier you entered is already in use. Verify that the information is accurate.National IDs (Row 3)This national identifier you entered is already in use. Verify that the information is accurate. &amp; find failed Screenshot Path:-&gt;H:\Clone-Workday-Playwright/WorkdayFailedScreenshot/2025-08-05T07-02-58-637Z.png</t>
   </si>
   <si>
     <t>420 Store Management (Rilyv Zisozy (4206015))</t>
   </si>
   <si>
-    <t>Priscilla</t>
-  </si>
-  <si>
-    <t>Harris</t>
+    <t>Itzel</t>
+  </si>
+  <si>
+    <t>Grant</t>
   </si>
   <si>
     <t>Sra.</t>
@@ -376,7 +370,7 @@
     <t>New</t>
   </si>
   <si>
-    <t>Auto 45418520</t>
+    <t>Auto 56662231</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -394,7 +388,7 @@
     <t>Single</t>
   </si>
   <si>
-    <t>24983028 3AP07</t>
+    <t>24983028 3AP25</t>
   </si>
 </sst>
 </file>
@@ -520,18 +514,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,7 +570,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -609,8 +604,8 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -618,7 +613,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -639,7 +634,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -683,9 +678,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -966,7 +965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BO16"/>
+  <dimension ref="A1:BO126"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.36328125" customWidth="1"/>
@@ -1244,422 +1243,422 @@
       <c r="A2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="12">
+        <v>10700457</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="E2" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="F2" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="G2" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="H2" s="18" t="s">
         <v>70</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>71</v>
       </c>
       <c r="I2" s="19">
         <v>234456532</v>
       </c>
       <c r="J2" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" s="19" t="s">
         <v>72</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>73</v>
       </c>
       <c r="L2" s="20">
         <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45821</v>
+        <v>45843</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N2" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="O2" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="P2" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="P2" s="21" t="s">
+      <c r="Q2" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="R2" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="Q2" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="R2" s="22" t="s">
+      <c r="S2" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="S2" s="23" t="s">
-        <v>78</v>
-      </c>
       <c r="T2" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U2" s="20">
         <f t="shared" ref="U2:U3" si="1">L2</f>
-        <v>45821</v>
+        <v>45843</v>
       </c>
       <c r="V2" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="W2" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="W2" s="24" t="s">
+      <c r="X2" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="X2" s="22" t="s">
+      <c r="Y2" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="Y2" s="25" t="s">
+      <c r="Z2" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="Z2" s="22" t="s">
+      <c r="AA2" s="26" t="s">
         <v>83</v>
-      </c>
-      <c r="AA2" s="26" t="s">
-        <v>84</v>
       </c>
       <c r="AB2" s="15">
         <v>40</v>
       </c>
       <c r="AC2" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD2" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="AD2" s="15" t="s">
+      <c r="AE2" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="AE2" s="20" t="s">
+      <c r="AF2" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="AF2" s="19" t="s">
+      <c r="AG2" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="AG2" s="28" t="s">
+      <c r="AH2" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="AH2" s="19" t="s">
+      <c r="AI2" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AI2" s="29" t="s">
+      <c r="AJ2" s="29" t="s">
         <v>91</v>
-      </c>
-      <c r="AJ2" s="29" t="s">
-        <v>92</v>
       </c>
       <c r="AK2" s="19">
         <v>99</v>
       </c>
       <c r="AL2" s="22">
         <f t="shared" ref="AL2:AL3" si="2">TODAY()+60</f>
-        <v>45912</v>
+        <v>45934</v>
       </c>
       <c r="AM2" s="22">
         <f t="shared" ref="AM2:AM3" si="3">U2</f>
-        <v>45821</v>
+        <v>45843</v>
       </c>
       <c r="AN2" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO2" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="AO2" s="21" t="s">
+      <c r="AP2" s="22" t="s">
         <v>94</v>
-      </c>
-      <c r="AP2" s="22" t="s">
-        <v>95</v>
       </c>
       <c r="AQ2" s="20">
         <f t="shared" ref="AQ2:AQ3" si="4">AE2</f>
         <v>NaN</v>
       </c>
       <c r="AR2" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="AS2" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="AS2" s="15" t="s">
+      <c r="AT2" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="AT2" s="15" t="s">
+      <c r="AU2" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="AV2" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="AU2" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="AV2" s="31" t="s">
+      <c r="AW2" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="AW2" s="22" t="s">
+      <c r="AX2" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="AY2" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="AX2" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="AY2" s="31" t="s">
+      <c r="AZ2" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA2" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="AZ2" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="BA2" s="32" t="s">
+      <c r="BB2" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="BB2" s="22" t="s">
+      <c r="BC2" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="BD2" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE2" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="BC2" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="BD2" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="BE2" s="33" t="s">
+      <c r="BF2" s="34">
+        <v>10000895933</v>
+      </c>
+      <c r="BG2" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="BH2" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="BF2" s="34">
-        <v>10000895911</v>
-      </c>
-      <c r="BG2" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH2" s="33" t="s">
+      <c r="BI2" s="34">
+        <v>100845964</v>
+      </c>
+      <c r="BJ2" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK2" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="BI2" s="34">
-        <v>100845944</v>
-      </c>
-      <c r="BJ2" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="BK2" s="35" t="s">
+      <c r="BL2" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="BL2" s="36" t="s">
+      <c r="BM2" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="BM2" s="33" t="s">
+      <c r="BN2" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="BN2" s="33" t="s">
+      <c r="BO2" s="33" t="s">
         <v>109</v>
-      </c>
-      <c r="BO2" s="33" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="3" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="12">
+        <v>10700458</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="D3" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="E3" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="G3" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3" s="16" t="s">
+      <c r="H3" s="18" t="s">
         <v>115</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>117</v>
       </c>
       <c r="I3" s="19">
         <v>234456532</v>
       </c>
       <c r="J3" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="K3" s="19" t="s">
         <v>72</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>73</v>
       </c>
       <c r="L3" s="20">
         <f t="shared" si="0"/>
-        <v>45821</v>
+        <v>45843</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N3" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="O3" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="O3" s="18" t="s">
+      <c r="P3" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="P3" s="21" t="s">
+      <c r="Q3" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="R3" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="Q3" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="R3" s="22" t="s">
+      <c r="S3" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="S3" s="23" t="s">
-        <v>78</v>
-      </c>
       <c r="T3" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U3" s="20">
         <f t="shared" si="1"/>
-        <v>45821</v>
+        <v>45843</v>
       </c>
       <c r="V3" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="W3" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="X3" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y3" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="W3" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="X3" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y3" s="25" t="s">
-        <v>120</v>
-      </c>
       <c r="Z3" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA3" s="26" t="s">
         <v>83</v>
-      </c>
-      <c r="AA3" s="26" t="s">
-        <v>84</v>
       </c>
       <c r="AB3" s="15">
         <v>40</v>
       </c>
       <c r="AC3" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD3" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="AD3" s="15" t="s">
+      <c r="AE3" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="AE3" s="20" t="s">
-        <v>87</v>
-      </c>
       <c r="AF3" s="19" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AG3" s="38">
         <v>251</v>
       </c>
       <c r="AH3" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI3" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AI3" s="29" t="s">
+      <c r="AJ3" s="29" t="s">
         <v>91</v>
-      </c>
-      <c r="AJ3" s="29" t="s">
-        <v>92</v>
       </c>
       <c r="AK3" s="19">
         <v>99</v>
       </c>
       <c r="AL3" s="22">
         <f t="shared" si="2"/>
-        <v>45912</v>
+        <v>45934</v>
       </c>
       <c r="AM3" s="22">
         <f t="shared" si="3"/>
-        <v>45821</v>
+        <v>45843</v>
       </c>
       <c r="AN3" s="30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AO3" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP3" s="22" t="s">
         <v>94</v>
-      </c>
-      <c r="AP3" s="22" t="s">
-        <v>95</v>
       </c>
       <c r="AQ3" s="20">
         <f t="shared" si="4"/>
         <v>NaN</v>
       </c>
       <c r="AR3" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AS3" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AT3" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AU3" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AV3" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW3" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="AX3" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="AY3" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="AZ3" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA3" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="BB3" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC3" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="BD3" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="BE3" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="BF3" s="34">
+        <v>10000895934</v>
+      </c>
+      <c r="BG3" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="BH3" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="BI3" s="34">
+        <v>100845965</v>
+      </c>
+      <c r="BJ3" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="BK3" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="BL3" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="AW3" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="AX3" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="AY3" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="AZ3" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="BA3" s="32" t="s">
-        <v>124</v>
-      </c>
-      <c r="BB3" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="BC3" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="BD3" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="BE3" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="BF3" s="34">
-        <v>10000895912</v>
-      </c>
-      <c r="BG3" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="BH3" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="BI3" s="34">
-        <v>100845945</v>
-      </c>
-      <c r="BJ3" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="BK3" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="BL3" s="36" t="s">
-        <v>125</v>
-      </c>
       <c r="BM3" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="BN3" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="BN3" s="33" t="s">
+      <c r="BO3" s="33" t="s">
         <v>109</v>
-      </c>
-      <c r="BO3" s="33" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="4" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
       <c r="D4" s="14"/>
       <c r="E4" s="15"/>
       <c r="F4" s="16"/>
@@ -1727,8 +1726,8 @@
     </row>
     <row r="5" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
       <c r="D5" s="14"/>
       <c r="E5" s="15"/>
       <c r="F5" s="16"/>
@@ -1749,7 +1748,7 @@
       <c r="U5" s="20"/>
       <c r="V5" s="19"/>
       <c r="W5" s="24"/>
-      <c r="X5" s="39"/>
+      <c r="X5" s="40"/>
       <c r="Y5" s="25"/>
       <c r="Z5" s="22"/>
       <c r="AA5" s="26"/>
@@ -1796,8 +1795,8 @@
     </row>
     <row r="6" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="37"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
       <c r="D6" s="14"/>
       <c r="E6" s="15"/>
       <c r="F6" s="16"/>
@@ -1864,8 +1863,8 @@
     </row>
     <row r="7" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="37"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
       <c r="D7" s="14"/>
       <c r="E7" s="15"/>
       <c r="F7" s="16"/>
@@ -1933,8 +1932,8 @@
     </row>
     <row r="8" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="37"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
       <c r="D8" s="14"/>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
@@ -1955,7 +1954,7 @@
       <c r="U8" s="20"/>
       <c r="V8" s="19"/>
       <c r="W8" s="24"/>
-      <c r="X8" s="39"/>
+      <c r="X8" s="40"/>
       <c r="Y8" s="25"/>
       <c r="Z8" s="22"/>
       <c r="AA8" s="26"/>
@@ -2002,8 +2001,8 @@
     </row>
     <row r="9" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="37"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
       <c r="D9" s="14"/>
       <c r="E9" s="15"/>
       <c r="F9" s="16"/>
@@ -2024,7 +2023,7 @@
       <c r="U9" s="20"/>
       <c r="V9" s="19"/>
       <c r="W9" s="24"/>
-      <c r="X9" s="39"/>
+      <c r="X9" s="40"/>
       <c r="Y9" s="25"/>
       <c r="Z9" s="22"/>
       <c r="AA9" s="26"/>
@@ -2071,8 +2070,8 @@
     </row>
     <row r="10" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="37"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
       <c r="D10" s="14"/>
       <c r="E10" s="15"/>
       <c r="F10" s="16"/>
@@ -2140,8 +2139,8 @@
     </row>
     <row r="11" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="37"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
       <c r="D11" s="14"/>
       <c r="E11" s="15"/>
       <c r="F11" s="16"/>
@@ -2209,8 +2208,8 @@
     </row>
     <row r="12" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
       <c r="D12" s="14"/>
       <c r="E12" s="15"/>
       <c r="F12" s="16"/>
@@ -2278,8 +2277,8 @@
     </row>
     <row r="13" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
       <c r="D13" s="14"/>
       <c r="E13" s="15"/>
       <c r="F13" s="16"/>
@@ -2300,7 +2299,7 @@
       <c r="U13" s="20"/>
       <c r="V13" s="19"/>
       <c r="W13" s="24"/>
-      <c r="X13" s="39"/>
+      <c r="X13" s="40"/>
       <c r="Y13" s="25"/>
       <c r="Z13" s="22"/>
       <c r="AA13" s="26"/>
@@ -2347,8 +2346,8 @@
     </row>
     <row r="14" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="37"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
       <c r="D14" s="14"/>
       <c r="E14" s="15"/>
       <c r="F14" s="16"/>
@@ -2416,8 +2415,8 @@
     </row>
     <row r="15" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="37"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
       <c r="D15" s="14"/>
       <c r="E15" s="15"/>
       <c r="F15" s="16"/>
@@ -2485,8 +2484,8 @@
     </row>
     <row r="16" ht="17.4" customHeight="1" spans="1:67" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="37"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
       <c r="D16" s="14"/>
       <c r="E16" s="15"/>
       <c r="F16" s="16"/>
@@ -2552,6 +2551,446 @@
       <c r="BN16" s="33"/>
       <c r="BO16" s="33"/>
     </row>
+    <row r="17" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+    </row>
+    <row r="18" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+    </row>
+    <row r="19" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+    </row>
+    <row r="20" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+    </row>
+    <row r="21" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+    </row>
+    <row r="22" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+    </row>
+    <row r="23" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+    </row>
+    <row r="24" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+    </row>
+    <row r="25" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+    </row>
+    <row r="26" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+    </row>
+    <row r="27" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+    </row>
+    <row r="28" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+    </row>
+    <row r="29" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+    </row>
+    <row r="30" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+    </row>
+    <row r="31" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+    </row>
+    <row r="32" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="41"/>
+      <c r="C32" s="41"/>
+    </row>
+    <row r="33" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+    </row>
+    <row r="34" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="41"/>
+      <c r="C34" s="41"/>
+    </row>
+    <row r="35" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="41"/>
+      <c r="C35" s="41"/>
+    </row>
+    <row r="36" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="41"/>
+      <c r="C36" s="41"/>
+    </row>
+    <row r="37" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="41"/>
+      <c r="C37" s="41"/>
+    </row>
+    <row r="38" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="41"/>
+      <c r="C38" s="41"/>
+    </row>
+    <row r="39" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="41"/>
+      <c r="C39" s="41"/>
+    </row>
+    <row r="40" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="41"/>
+      <c r="C40" s="41"/>
+    </row>
+    <row r="41" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="41"/>
+      <c r="C41" s="41"/>
+    </row>
+    <row r="42" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="41"/>
+      <c r="C42" s="41"/>
+    </row>
+    <row r="43" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="41"/>
+      <c r="C43" s="41"/>
+    </row>
+    <row r="44" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="41"/>
+      <c r="C44" s="41"/>
+    </row>
+    <row r="45" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="41"/>
+      <c r="C45" s="41"/>
+    </row>
+    <row r="46" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="41"/>
+      <c r="C46" s="41"/>
+    </row>
+    <row r="47" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="41"/>
+      <c r="C47" s="41"/>
+    </row>
+    <row r="48" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="41"/>
+      <c r="C48" s="41"/>
+    </row>
+    <row r="49" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="41"/>
+      <c r="C49" s="41"/>
+    </row>
+    <row r="50" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="41"/>
+      <c r="C50" s="41"/>
+    </row>
+    <row r="51" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="41"/>
+      <c r="C51" s="41"/>
+    </row>
+    <row r="52" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="41"/>
+      <c r="C52" s="41"/>
+    </row>
+    <row r="53" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="41"/>
+      <c r="C53" s="41"/>
+    </row>
+    <row r="54" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="41"/>
+      <c r="C54" s="41"/>
+    </row>
+    <row r="55" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="41"/>
+      <c r="C55" s="41"/>
+    </row>
+    <row r="56" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="41"/>
+      <c r="C56" s="41"/>
+    </row>
+    <row r="57" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="41"/>
+      <c r="C57" s="41"/>
+    </row>
+    <row r="58" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="41"/>
+      <c r="C58" s="41"/>
+    </row>
+    <row r="59" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="41"/>
+      <c r="C59" s="41"/>
+    </row>
+    <row r="60" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="41"/>
+      <c r="C60" s="41"/>
+    </row>
+    <row r="61" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="41"/>
+      <c r="C61" s="41"/>
+    </row>
+    <row r="62" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="41"/>
+      <c r="C62" s="41"/>
+    </row>
+    <row r="63" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="41"/>
+      <c r="C63" s="41"/>
+    </row>
+    <row r="64" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="41"/>
+      <c r="C64" s="41"/>
+    </row>
+    <row r="65" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="41"/>
+      <c r="C65" s="41"/>
+    </row>
+    <row r="66" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="41"/>
+      <c r="C66" s="41"/>
+    </row>
+    <row r="67" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B67" s="41"/>
+      <c r="C67" s="41"/>
+    </row>
+    <row r="68" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B68" s="41"/>
+      <c r="C68" s="41"/>
+    </row>
+    <row r="69" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B69" s="41"/>
+      <c r="C69" s="41"/>
+    </row>
+    <row r="70" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B70" s="41"/>
+      <c r="C70" s="41"/>
+    </row>
+    <row r="71" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="41"/>
+      <c r="C71" s="41"/>
+    </row>
+    <row r="72" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="41"/>
+      <c r="C72" s="41"/>
+    </row>
+    <row r="73" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="41"/>
+      <c r="C73" s="41"/>
+    </row>
+    <row r="74" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B74" s="41"/>
+      <c r="C74" s="41"/>
+    </row>
+    <row r="75" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B75" s="41"/>
+      <c r="C75" s="41"/>
+    </row>
+    <row r="76" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B76" s="41"/>
+      <c r="C76" s="41"/>
+    </row>
+    <row r="77" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B77" s="41"/>
+      <c r="C77" s="41"/>
+    </row>
+    <row r="78" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B78" s="41"/>
+      <c r="C78" s="41"/>
+    </row>
+    <row r="79" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B79" s="41"/>
+      <c r="C79" s="41"/>
+    </row>
+    <row r="80" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B80" s="41"/>
+      <c r="C80" s="41"/>
+    </row>
+    <row r="81" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B81" s="41"/>
+      <c r="C81" s="41"/>
+    </row>
+    <row r="82" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B82" s="41"/>
+      <c r="C82" s="41"/>
+    </row>
+    <row r="83" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B83" s="41"/>
+      <c r="C83" s="41"/>
+    </row>
+    <row r="84" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B84" s="41"/>
+      <c r="C84" s="41"/>
+    </row>
+    <row r="85" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B85" s="41"/>
+      <c r="C85" s="41"/>
+    </row>
+    <row r="86" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B86" s="41"/>
+      <c r="C86" s="41"/>
+    </row>
+    <row r="87" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B87" s="41"/>
+      <c r="C87" s="41"/>
+    </row>
+    <row r="88" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B88" s="41"/>
+      <c r="C88" s="41"/>
+    </row>
+    <row r="89" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B89" s="41"/>
+      <c r="C89" s="41"/>
+    </row>
+    <row r="90" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B90" s="41"/>
+      <c r="C90" s="41"/>
+    </row>
+    <row r="91" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B91" s="41"/>
+      <c r="C91" s="41"/>
+    </row>
+    <row r="92" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B92" s="41"/>
+      <c r="C92" s="41"/>
+    </row>
+    <row r="93" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B93" s="41"/>
+      <c r="C93" s="41"/>
+    </row>
+    <row r="94" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B94" s="41"/>
+      <c r="C94" s="41"/>
+    </row>
+    <row r="95" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B95" s="41"/>
+      <c r="C95" s="41"/>
+    </row>
+    <row r="96" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B96" s="41"/>
+      <c r="C96" s="41"/>
+    </row>
+    <row r="97" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B97" s="41"/>
+      <c r="C97" s="41"/>
+    </row>
+    <row r="98" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B98" s="41"/>
+      <c r="C98" s="41"/>
+    </row>
+    <row r="99" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B99" s="41"/>
+      <c r="C99" s="41"/>
+    </row>
+    <row r="100" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B100" s="41"/>
+      <c r="C100" s="41"/>
+    </row>
+    <row r="101" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B101" s="41"/>
+      <c r="C101" s="41"/>
+    </row>
+    <row r="102" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B102" s="41"/>
+      <c r="C102" s="41"/>
+    </row>
+    <row r="103" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B103" s="41"/>
+      <c r="C103" s="41"/>
+    </row>
+    <row r="104" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B104" s="41"/>
+      <c r="C104" s="41"/>
+    </row>
+    <row r="105" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B105" s="41"/>
+      <c r="C105" s="41"/>
+    </row>
+    <row r="106" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B106" s="41"/>
+      <c r="C106" s="41"/>
+    </row>
+    <row r="107" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B107" s="41"/>
+      <c r="C107" s="41"/>
+    </row>
+    <row r="108" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B108" s="41"/>
+      <c r="C108" s="41"/>
+    </row>
+    <row r="109" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B109" s="41"/>
+      <c r="C109" s="41"/>
+    </row>
+    <row r="110" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B110" s="41"/>
+      <c r="C110" s="41"/>
+    </row>
+    <row r="111" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B111" s="41"/>
+      <c r="C111" s="41"/>
+    </row>
+    <row r="112" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B112" s="41"/>
+      <c r="C112" s="41"/>
+    </row>
+    <row r="113" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B113" s="41"/>
+      <c r="C113" s="41"/>
+    </row>
+    <row r="114" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B114" s="41"/>
+      <c r="C114" s="41"/>
+    </row>
+    <row r="115" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B115" s="41"/>
+      <c r="C115" s="41"/>
+    </row>
+    <row r="116" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B116" s="41"/>
+      <c r="C116" s="41"/>
+    </row>
+    <row r="117" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B117" s="41"/>
+      <c r="C117" s="41"/>
+    </row>
+    <row r="118" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B118" s="41"/>
+      <c r="C118" s="41"/>
+    </row>
+    <row r="119" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B119" s="41"/>
+      <c r="C119" s="41"/>
+    </row>
+    <row r="120" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B120" s="41"/>
+      <c r="C120" s="41"/>
+    </row>
+    <row r="121" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B121" s="41"/>
+      <c r="C121" s="41"/>
+    </row>
+    <row r="122" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B122" s="41"/>
+      <c r="C122" s="41"/>
+    </row>
+    <row r="123" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B123" s="41"/>
+      <c r="C123" s="41"/>
+    </row>
+    <row r="124" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B124" s="41"/>
+      <c r="C124" s="41"/>
+    </row>
+    <row r="125" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B125" s="41"/>
+      <c r="C125" s="41"/>
+    </row>
+    <row r="126" ht="14.4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B126" s="41"/>
+      <c r="C126" s="41"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="S2" r:id="rId1"/>
